--- a/hrms/Contract_Template_Excel.xlsx
+++ b/hrms/Contract_Template_Excel.xlsx
@@ -147,7 +147,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -176,13 +176,6 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -190,6 +183,7 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -250,15 +244,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -280,17 +274,18 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="13.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="19.62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="10.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="17.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="17.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="17.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="15.54"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="14.33"/>
@@ -298,7 +293,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="18.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="20.4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="20.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="16.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="16.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="22.6"/>
   </cols>
   <sheetData>
